--- a/data/trending_integrated_20260911_09.xlsx
+++ b/data/trending_integrated_20260911_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,60 +563,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49750</v>
+        <v>16180</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>+11.51%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.09</v>
+        <v>3.11</v>
       </c>
       <c r="E2" t="n">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="F2" t="n">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="G2" t="n">
-        <v>243</v>
+        <v>516</v>
       </c>
       <c r="H2" t="n">
-        <v>38.78</v>
+        <v>3.14</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>50400</v>
+        <v>14510</v>
       </c>
       <c r="K2" t="n">
-        <v>50500</v>
+        <v>17010</v>
       </c>
       <c r="L2" t="n">
-        <v>50600</v>
+        <v>17310</v>
       </c>
       <c r="M2" t="n">
-        <v>49650</v>
+        <v>16020</v>
       </c>
       <c r="N2" t="n">
-        <v>38.69</v>
+        <v>0.03</v>
       </c>
       <c r="O2" t="n">
-        <v>7367118700</v>
+        <v>69170154900</v>
       </c>
       <c r="P2" t="n">
-        <v>67300</v>
+        <v>36200</v>
       </c>
       <c r="Q2" t="n">
-        <v>23150</v>
+        <v>8920</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,20 +626,20 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>삼성E&amp;A, 약 4.7조원 규모의 대형 수주 공시. 사우디 및 베트남 관련 호재.</t>
+          <t>국제 유가 급등 및 중동 전쟁 관련 보도를 바탕으로 한 기대감 표출. 3연상 목표.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['수주 공시', '계약금액', '사우디']</t>
+          <t>['국제 유가', '중동 전쟁', '폭등']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,67 +648,67 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>405000</v>
+        <v>26450</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.99%</t>
+          <t>+1.34%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.2</v>
+        <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G3" t="n">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="H3" t="n">
-        <v>38.02</v>
+        <v>0.32</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>417500</v>
+        <v>26100</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>26350</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>27300</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>25400</v>
       </c>
       <c r="N3" t="n">
-        <v>37.82</v>
+        <v>0.33</v>
       </c>
       <c r="O3" t="n">
-        <v>9576000000</v>
+        <v>26955027850</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>39350</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -718,20 +718,20 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>현대모비스, 유럽 최대 규모 PE 시스템 공장 가동 및 로봇 사업 진출. 유럽 중국차 관세 부과로 인한 반사이익 기대.</t>
+          <t>신규주 관련 혼조된 기대감 및 하락 가능성 언급. 뚜렷한 근거 부재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['PE 시스템', '로봇 사업', '반사이익']</t>
+          <t>['신규주', '단타', '상한가']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19160</v>
+        <v>89300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.99%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="E4" t="n">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="G4" t="n">
-        <v>176</v>
+        <v>572</v>
       </c>
       <c r="H4" t="n">
-        <v>10.65</v>
+        <v>23.59</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,28 +779,28 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>19750</v>
+        <v>89900</v>
       </c>
       <c r="K4" t="n">
-        <v>19500</v>
+        <v>88700</v>
       </c>
       <c r="L4" t="n">
-        <v>19510</v>
+        <v>90400</v>
       </c>
       <c r="M4" t="n">
-        <v>19060</v>
+        <v>88000</v>
       </c>
       <c r="N4" t="n">
-        <v>10.64</v>
+        <v>23.65</v>
       </c>
       <c r="O4" t="n">
-        <v>4425553760</v>
+        <v>30721342550</v>
       </c>
       <c r="P4" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q4" t="n">
-        <v>3320</v>
+        <v>57000</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -810,20 +810,20 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>NH투자증권, 대우건설 목표주가 3만원으로 상향. 대차해지 관련 논의.</t>
+          <t>에너지 대미 투자 협상 마무리 및 수주 잔고 규모 증가 관련 긍정적 전망. 월스트리트저널 보도 인용.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['목표주가 상향', '대차해지', 'NH투자증권']</t>
+          <t>['수주잔고', '투자 협상', '에너지']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>237000</v>
+        <v>50400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-5.39%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.96</v>
+        <v>0.09</v>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>194</v>
+        <v>263</v>
       </c>
       <c r="H5" t="n">
-        <v>7.58</v>
+        <v>38.78</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>250500</v>
+        <v>50800</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -883,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>8.539999999999999</v>
+        <v>38.69</v>
       </c>
       <c r="O5" t="n">
-        <v>14313000000</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -902,27 +902,487 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>한미반도체 1분기 영업이익 -88%로 주가 폭락 불가피. 공매도 및 외국인 매도세에 대한 우려.</t>
+          <t>약 4.7조원 규모의 대형 수주 공시 확인. 사우디, 베트남 관련 겹호재 및 상승 추세 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>['대형 수주', '공시', '상승 추세']</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>현대모비스</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>410500</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-1.20%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>0.2</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>['영업이익', '폭락', '공매도']</t>
-        </is>
-      </c>
-      <c r="X5" t="n">
+      <c r="E6" t="n">
+        <v>49</v>
+      </c>
+      <c r="F6" t="n">
+        <v>33</v>
+      </c>
+      <c r="G6" t="n">
+        <v>126</v>
+      </c>
+      <c r="H6" t="n">
+        <v>38.02</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>415500</v>
+      </c>
+      <c r="K6" t="n">
+        <v>407000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>412000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>404000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>37.82</v>
+      </c>
+      <c r="O6" t="n">
+        <v>14883204750</v>
+      </c>
+      <c r="P6" t="n">
+        <v>822000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>283000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>로봇 및 미래차 신기술 공개, 유럽 중국차 관세 관련 호재 언급. 개인 투자자들의 매수세 관찰.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['로봇', '미래차', '관세']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
         <v>1</v>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>012330</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>19450</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-1.52%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E7" t="n">
+        <v>45</v>
+      </c>
+      <c r="F7" t="n">
+        <v>37</v>
+      </c>
+      <c r="G7" t="n">
+        <v>193</v>
+      </c>
+      <c r="H7" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>19750</v>
+      </c>
+      <c r="K7" t="n">
+        <v>19500</v>
+      </c>
+      <c r="L7" t="n">
+        <v>19800</v>
+      </c>
+      <c r="M7" t="n">
+        <v>19060</v>
+      </c>
+      <c r="N7" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="O7" t="n">
+        <v>20492558010</v>
+      </c>
+      <c r="P7" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>NH투자증권의 목표주가 상향 조정 및 미국 투자 마무리 협상 관련 긍정적 소식. 대차해지 관련 언급.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['목표주가 상향', '투자 협상', '대차해지']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>258750</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-3.81%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>800</v>
+      </c>
+      <c r="F8" t="n">
+        <v>502</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2668</v>
+      </c>
+      <c r="H8" t="n">
+        <v>46.71</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>269000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>258000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>260000</v>
+      </c>
+      <c r="M8" t="n">
+        <v>257500</v>
+      </c>
+      <c r="N8" t="n">
+        <v>46.81</v>
+      </c>
+      <c r="O8" t="n">
+        <v>342679194750</v>
+      </c>
+      <c r="P8" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>72100</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>미국 증시 하락 및 금리 인상 우려 속 부정적 전망 제시. AI 생태계 변화 관련 뉴스 언급.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['AI', '반도체', 'FOMC']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>104</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>페니트리움바이오</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7920</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-4.58%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E9" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" t="n">
+        <v>33</v>
+      </c>
+      <c r="G9" t="n">
+        <v>332</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>8300</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8400</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8700</v>
+      </c>
+      <c r="M9" t="n">
+        <v>7720</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="O9" t="n">
+        <v>6503413280</v>
+      </c>
+      <c r="P9" t="n">
+        <v>21500</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2300</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>임상 시험 디자인 및 기술 수출 가능성 언급. 투자 주의 종목 지정.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['임상 시험', '기술 수출', '투자 주의']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>187660</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>한미반도체</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>233500</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-7.71%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="E10" t="n">
+        <v>73</v>
+      </c>
+      <c r="F10" t="n">
+        <v>47</v>
+      </c>
+      <c r="G10" t="n">
+        <v>244</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>253000</v>
+      </c>
+      <c r="K10" t="n">
+        <v>241000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>241000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>231000</v>
+      </c>
+      <c r="N10" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="O10" t="n">
+        <v>49777101750</v>
+      </c>
+      <c r="P10" t="n">
+        <v>426000</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>86100</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>CPI 발표 이후 조정 예상 및 외국인 매도세 관찰. 주가 하락에 대한 부정적 전망.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['CPI', '공매도', '수주']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>042700</t>
         </is>

--- a/data/trending_integrated_20260911_09.xlsx
+++ b/data/trending_integrated_20260911_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16180</v>
+        <v>15910</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+11.51%</t>
+          <t>+9.65%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>3.11</v>
       </c>
       <c r="E2" t="n">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="F2" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="G2" t="n">
-        <v>516</v>
+        <v>552</v>
       </c>
       <c r="H2" t="n">
         <v>3.14</v>
@@ -604,13 +604,13 @@
         <v>17310</v>
       </c>
       <c r="M2" t="n">
-        <v>16020</v>
+        <v>15820</v>
       </c>
       <c r="N2" t="n">
         <v>0.03</v>
       </c>
       <c r="O2" t="n">
-        <v>69170154900</v>
+        <v>92096057920</v>
       </c>
       <c r="P2" t="n">
         <v>36200</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>국제 유가 급등 및 중동 전쟁 관련 보도를 바탕으로 한 기대감 표출. 3연상 목표.</t>
+          <t>중동 전쟁 및 유가 폭등으로 인한 급등 기대감. WTI 100달러 돌파 및 3연상 목표.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['국제 유가', '중동 전쟁', '폭등']</t>
+          <t>['유가 폭등', '중동 전쟁', '3연상']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26450</v>
+        <v>27900</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+1.34%</t>
+          <t>+6.90%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="F3" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="H3" t="n">
         <v>0.32</v>
@@ -693,7 +693,7 @@
         <v>26350</v>
       </c>
       <c r="L3" t="n">
-        <v>27300</v>
+        <v>28800</v>
       </c>
       <c r="M3" t="n">
         <v>25400</v>
@@ -702,7 +702,7 @@
         <v>0.33</v>
       </c>
       <c r="O3" t="n">
-        <v>26955027850</v>
+        <v>77062111250</v>
       </c>
       <c r="P3" t="n">
         <v>39350</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>신규주 관련 혼조된 기대감 및 하락 가능성 언급. 뚜렷한 근거 부재.</t>
+          <t>신규주로서의 상승 기대감. 3일간 조정 후 수급 개선 및 상한가 예상.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['신규주', '단타', '상한가']</t>
+          <t>['신규주', '수급 개선', '상한가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>89300</v>
+        <v>1976</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>+3.95%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.06</v>
+        <v>0.32</v>
       </c>
       <c r="E4" t="n">
-        <v>111</v>
+        <v>45</v>
       </c>
       <c r="F4" t="n">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>572</v>
+        <v>82</v>
       </c>
       <c r="H4" t="n">
-        <v>23.59</v>
+        <v>2.44</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,28 +779,28 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>89900</v>
+        <v>1901</v>
       </c>
       <c r="K4" t="n">
-        <v>88700</v>
+        <v>2050</v>
       </c>
       <c r="L4" t="n">
-        <v>90400</v>
+        <v>2080</v>
       </c>
       <c r="M4" t="n">
-        <v>88000</v>
+        <v>1961</v>
       </c>
       <c r="N4" t="n">
-        <v>23.65</v>
+        <v>2.12</v>
       </c>
       <c r="O4" t="n">
-        <v>30721342550</v>
+        <v>21942170707</v>
       </c>
       <c r="P4" t="n">
-        <v>139200</v>
+        <v>4795</v>
       </c>
       <c r="Q4" t="n">
-        <v>57000</v>
+        <v>1524</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -810,20 +810,20 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>에너지 대미 투자 협상 마무리 및 수주 잔고 규모 증가 관련 긍정적 전망. 월스트리트저널 보도 인용.</t>
+          <t>전쟁 테마주로 분류되어 유가 상승에 따른 급등 기대감. 2500원 목표가 제시.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['수주잔고', '투자 협상', '에너지']</t>
+          <t>['전쟁 테마주', '유가 상승', '목표가']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50400</v>
+        <v>19680</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+1.18%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="E5" t="n">
         <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>263</v>
+        <v>213</v>
       </c>
       <c r="H5" t="n">
-        <v>38.78</v>
+        <v>10.65</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>50800</v>
+        <v>19450</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -883,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>38.69</v>
+        <v>10.64</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>29883000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -902,20 +902,20 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모의 대형 수주 공시 확인. 사우디, 베트남 관련 겹호재 및 상승 추세 언급.</t>
+          <t>NH투자증권의 목표주가 상향 및 대차해지 운동 언급. 2만원 이상 거래 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['대형 수주', '공시', '상승 추세']</t>
+          <t>['NH투자증권', '목표주가 상향', '대차해지']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,67 +924,67 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>410500</v>
+        <v>14300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.2</v>
+        <v>-0.11</v>
       </c>
       <c r="E6" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>126</v>
+        <v>268</v>
       </c>
       <c r="H6" t="n">
-        <v>38.02</v>
+        <v>5.98</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>415500</v>
+        <v>14320</v>
       </c>
       <c r="K6" t="n">
-        <v>407000</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>412000</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>404000</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>37.82</v>
+        <v>6.09</v>
       </c>
       <c r="O6" t="n">
-        <v>14883204750</v>
+        <v>40722000000</v>
       </c>
       <c r="P6" t="n">
-        <v>822000</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>283000</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>로봇 및 미래차 신기술 공개, 유럽 중국차 관세 관련 호재 언급. 개인 투자자들의 매수세 관찰.</t>
+          <t>원전 관련 모멘텀으로 인한 상승 기대감. 단기과열 예고 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['로봇', '미래차', '관세']</t>
+          <t>['원전', '모멘텀', '단기과열']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19450</v>
+        <v>50300</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.52%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="F7" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G7" t="n">
-        <v>193</v>
+        <v>327</v>
       </c>
       <c r="H7" t="n">
-        <v>10.65</v>
+        <v>38.78</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,28 +1055,28 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>19750</v>
+        <v>50400</v>
       </c>
       <c r="K7" t="n">
-        <v>19500</v>
+        <v>50500</v>
       </c>
       <c r="L7" t="n">
-        <v>19800</v>
+        <v>50600</v>
       </c>
       <c r="M7" t="n">
-        <v>19060</v>
+        <v>49650</v>
       </c>
       <c r="N7" t="n">
-        <v>10.64</v>
+        <v>38.69</v>
       </c>
       <c r="O7" t="n">
-        <v>20492558010</v>
+        <v>19599093325</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>67300</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>23150</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1086,20 +1086,20 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>NH투자증권의 목표주가 상향 조정 및 미국 투자 마무리 협상 관련 긍정적 소식. 대차해지 관련 언급.</t>
+          <t>약 4.7조원 규모의 대규모 수주 공시 확인. 외국인 지분율 소폭 상승.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['목표주가 상향', '투자 협상', '대차해지']</t>
+          <t>['수주', '공시', '외국인']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>258750</v>
+        <v>413500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.81%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>56</v>
       </c>
       <c r="F8" t="n">
-        <v>502</v>
+        <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>2668</v>
+        <v>136</v>
       </c>
       <c r="H8" t="n">
-        <v>46.71</v>
+        <v>38.02</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,28 +1147,28 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>269000</v>
+        <v>415500</v>
       </c>
       <c r="K8" t="n">
-        <v>258000</v>
+        <v>407000</v>
       </c>
       <c r="L8" t="n">
-        <v>260000</v>
+        <v>413500</v>
       </c>
       <c r="M8" t="n">
-        <v>257500</v>
+        <v>404000</v>
       </c>
       <c r="N8" t="n">
-        <v>46.81</v>
+        <v>37.82</v>
       </c>
       <c r="O8" t="n">
-        <v>342679194750</v>
+        <v>17582214500</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>822000</v>
       </c>
       <c r="Q8" t="n">
-        <v>72100</v>
+        <v>283000</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1178,20 +1178,20 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 증시 하락 및 금리 인상 우려 속 부정적 전망 제시. AI 생태계 변화 관련 뉴스 언급.</t>
+          <t>자동차 부품을 넘어 로봇 사업 확장 및 유럽 중국차 관세 이슈로 인한 호재. 글로벌 수주 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI', '반도체', 'FOMC']</t>
+          <t>['로봇 사업', '유럽 관세', '글로벌 수주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,67 +1200,67 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7920</v>
+        <v>89900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.58%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.12</v>
+        <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="G9" t="n">
-        <v>332</v>
+        <v>589</v>
       </c>
       <c r="H9" t="n">
-        <v>1.29</v>
+        <v>23.59</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>8300</v>
+        <v>91700</v>
       </c>
       <c r="K9" t="n">
-        <v>8400</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>7720</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.17</v>
+        <v>23.65</v>
       </c>
       <c r="O9" t="n">
-        <v>6503413280</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>21500</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1270,20 +1270,20 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>임상 시험 디자인 및 기술 수출 가능성 언급. 투자 주의 종목 지정.</t>
+          <t>에너지 대미 투자 협상 마무리 및 수주 잔고 규모 증가 관련 긍정적 전망. 월스트리트저널 보도 인용.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['임상 시험', '기술 수출', '투자 주의']</t>
+          <t>['수주잔고', '투자 협상', '에너지']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>233500</v>
+        <v>259000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-7.71%</t>
+          <t>-3.72%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.96</v>
+        <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>73</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>506</v>
       </c>
       <c r="G10" t="n">
-        <v>244</v>
+        <v>2709</v>
       </c>
       <c r="H10" t="n">
-        <v>7.58</v>
+        <v>46.71</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,28 +1331,28 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>253000</v>
+        <v>269000</v>
       </c>
       <c r="K10" t="n">
-        <v>241000</v>
+        <v>258000</v>
       </c>
       <c r="L10" t="n">
-        <v>241000</v>
+        <v>260000</v>
       </c>
       <c r="M10" t="n">
-        <v>231000</v>
+        <v>257500</v>
       </c>
       <c r="N10" t="n">
-        <v>8.539999999999999</v>
+        <v>46.81</v>
       </c>
       <c r="O10" t="n">
-        <v>49777101750</v>
+        <v>462813664500</v>
       </c>
       <c r="P10" t="n">
-        <v>426000</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>86100</v>
+        <v>72100</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>CPI 발표 이후 조정 예상 및 외국인 매도세 관찰. 주가 하락에 대한 부정적 전망.</t>
+          <t>미증시 하락 및 매크로 변수 영향으로 인한 부정적 전망. 15만 전자 가능성 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,18 +1371,294 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['CPI', '공매도', '수주']</t>
+          <t>['미증시 하락', '매크로 변수', '부정적 전망']</t>
         </is>
       </c>
       <c r="X10" t="n">
+        <v>104</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1775000</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-4.21%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="E11" t="n">
+        <v>800</v>
+      </c>
+      <c r="F11" t="n">
+        <v>497</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1853000</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1773000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1785000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1768000</v>
+      </c>
+      <c r="N11" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="O11" t="n">
+        <v>801119054000</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>305500</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>미국 증시 및 ADR 하락으로 인한 급락 우려. 오라클 실적 발표에 따른 변동성 예상.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['ADR 하락', '오라클 실적', '급락 우려']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>69</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>페니트리움바이오</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7920</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-4.58%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E12" t="n">
+        <v>64</v>
+      </c>
+      <c r="F12" t="n">
+        <v>40</v>
+      </c>
+      <c r="G12" t="n">
+        <v>390</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>8300</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8400</v>
+      </c>
+      <c r="L12" t="n">
+        <v>8700</v>
+      </c>
+      <c r="M12" t="n">
+        <v>7720</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="O12" t="n">
+        <v>7916378225</v>
+      </c>
+      <c r="P12" t="n">
+        <v>21500</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2300</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>임상시험 디자인 및 기술 수출 기대감. 동시호가 3% 이상 시 상한가 확률 언급.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['임상시험', '기술 수출', '상한가 확률']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>187660</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>한미반도체</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>233500</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-7.71%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="E13" t="n">
+        <v>89</v>
+      </c>
+      <c r="F13" t="n">
+        <v>55</v>
+      </c>
+      <c r="G13" t="n">
+        <v>312</v>
+      </c>
+      <c r="H13" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>253000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>241000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>241000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>231000</v>
+      </c>
+      <c r="N13" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="O13" t="n">
+        <v>63859079250</v>
+      </c>
+      <c r="P13" t="n">
+        <v>426000</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>86100</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>CPI 예상치 하회에도 불구하고 주가 하락. 공매도 및 곽동신 오판에 대한 부정적 시각.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['CPI', '공매도', '주가 하락']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
         <v>1</v>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>042700</t>
         </is>

--- a/data/trending_integrated_20260911_09.xlsx
+++ b/data/trending_integrated_20260911_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,83 +563,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15910</v>
+        <v>144300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+9.65%</t>
+          <t>+24.08%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.11</v>
+        <v>-0.26</v>
       </c>
       <c r="E2" t="n">
-        <v>173</v>
+        <v>49</v>
       </c>
       <c r="F2" t="n">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>552</v>
+        <v>67</v>
       </c>
       <c r="H2" t="n">
-        <v>3.14</v>
+        <v>4.32</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>14510</v>
+        <v>116300</v>
       </c>
       <c r="K2" t="n">
-        <v>17010</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>17310</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>15820</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03</v>
+        <v>4.58</v>
       </c>
       <c r="O2" t="n">
-        <v>92096057920</v>
+        <v>229740000000</v>
       </c>
       <c r="P2" t="n">
-        <v>36200</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>8920</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>중동 전쟁 및 유가 폭등으로 인한 급등 기대감. WTI 100달러 돌파 및 3연상 목표.</t>
+          <t>MLCC 수요 폭발 및 무라타 관련 이슈로 인한 주가 상승 기대. 애플, 삼성전기 등 연관 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['유가 폭등', '중동 전쟁', '3연상']</t>
+          <t>['MLCC', '삼화콘덴서', '무라타']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,77 +648,77 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>001820</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27900</v>
+        <v>1967</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+6.90%</t>
+          <t>+11.76%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.01</v>
+        <v>0.32</v>
       </c>
       <c r="E3" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32</v>
+        <v>2.44</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>26100</v>
+        <v>1760</v>
       </c>
       <c r="K3" t="n">
-        <v>26350</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>28800</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>25400</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.33</v>
+        <v>2.12</v>
       </c>
       <c r="O3" t="n">
-        <v>77062111250</v>
+        <v>24556000000</v>
       </c>
       <c r="P3" t="n">
-        <v>39350</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-846000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>신규주로서의 상승 기대감. 3일간 조정 후 수급 개선 및 상한가 예상.</t>
+          <t>국제 유가 상승에 따른 전쟁 테마주 부각 및 2500원 목표 홀드 의견. 일부 부정적 의견 존재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['신규주', '수급 개선', '상한가']</t>
+          <t>['전쟁테마주', '국제유가', '흥아해운']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1976</v>
+        <v>28950</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+3.95%</t>
+          <t>+10.92%</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E4" t="n">
+        <v>71</v>
+      </c>
+      <c r="F4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G4" t="n">
+        <v>109</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.32</v>
       </c>
-      <c r="E4" t="n">
-        <v>45</v>
-      </c>
-      <c r="F4" t="n">
-        <v>30</v>
-      </c>
-      <c r="G4" t="n">
-        <v>82</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.44</v>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1901</v>
+        <v>26100</v>
       </c>
       <c r="K4" t="n">
-        <v>2050</v>
+        <v>26350</v>
       </c>
       <c r="L4" t="n">
-        <v>2080</v>
+        <v>28950</v>
       </c>
       <c r="M4" t="n">
-        <v>1961</v>
+        <v>25400</v>
       </c>
       <c r="N4" t="n">
-        <v>2.12</v>
+        <v>0.33</v>
       </c>
       <c r="O4" t="n">
-        <v>21942170707</v>
+        <v>104372894700</v>
       </c>
       <c r="P4" t="n">
-        <v>4795</v>
+        <v>39350</v>
       </c>
       <c r="Q4" t="n">
-        <v>1524</v>
+        <v>8200</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>전쟁 테마주로 분류되어 유가 상승에 따른 급등 기대감. 2500원 목표가 제시.</t>
+          <t>신규 상장주로서 단기 조정 후 상승 기대감. 2차 번트 및 상한가 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['전쟁 테마주', '유가 상승', '목표가']</t>
+          <t>['스카이랩스', '신규주', '수급']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,77 +832,77 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19680</v>
+        <v>10170</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+1.18%</t>
+          <t>+9.59%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>213</v>
+        <v>150</v>
       </c>
       <c r="H5" t="n">
-        <v>10.65</v>
+        <v>4.49</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>19450</v>
+        <v>9280</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>10030</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>10880</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>10010</v>
       </c>
       <c r="N5" t="n">
-        <v>10.64</v>
+        <v>4.42</v>
       </c>
       <c r="O5" t="n">
-        <v>29883000000</v>
+        <v>15077490565</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>15640</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5470</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>NH투자증권의 목표주가 상향 및 대차해지 운동 언급. 2만원 이상 거래 기대.</t>
+          <t>프리갈리앙 베스트 의료기술상 수상 및 탈모약 관련 이슈. 호재 뉴스에도 주가 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['NH투자증권', '목표주가 상향', '대차해지']</t>
+          <t>['바이오니아', '프리갈리앙', '탈모약']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14300</v>
+        <v>15890</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+9.51%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.11</v>
+        <v>3.11</v>
       </c>
       <c r="E6" t="n">
-        <v>47</v>
+        <v>200</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="G6" t="n">
-        <v>268</v>
+        <v>572</v>
       </c>
       <c r="H6" t="n">
-        <v>5.98</v>
+        <v>3.14</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14320</v>
+        <v>14510</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>17010</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>17310</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>15690</v>
       </c>
       <c r="N6" t="n">
-        <v>6.09</v>
+        <v>0.03</v>
       </c>
       <c r="O6" t="n">
-        <v>40722000000</v>
+        <v>106942896195</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>36200</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>8920</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-268000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>원전 관련 모멘텀으로 인한 상승 기대감. 단기과열 예고 언급.</t>
+          <t>중동 전쟁 및 유가 폭등으로 인한 급등 기대감. WTI 100달러 돌파 및 3연상 목표.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전', '모멘텀', '단기과열']</t>
+          <t>['유가 폭등', '중동 전쟁', '3연상']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50300</v>
+        <v>7890</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>+6.33%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F7" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="G7" t="n">
-        <v>327</v>
+        <v>407</v>
       </c>
       <c r="H7" t="n">
-        <v>38.78</v>
+        <v>1.29</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>50400</v>
+        <v>7420</v>
       </c>
       <c r="K7" t="n">
-        <v>50500</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>50600</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>49650</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>38.69</v>
+        <v>1.17</v>
       </c>
       <c r="O7" t="n">
-        <v>19599093325</v>
+        <v>8749000000</v>
       </c>
       <c r="P7" t="n">
-        <v>67300</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>23150</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모의 대규모 수주 공시 확인. 외국인 지분율 소폭 상승.</t>
+          <t>임상시험 디자인 및 기술 수출 기대감. 동시호가 3% 이상 시 상한가 확률 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주', '공시', '외국인']</t>
+          <t>['임상시험', '기술 수출', '상한가 확률']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>413500</v>
+        <v>89700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2</v>
+        <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>56</v>
+        <v>130</v>
       </c>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="G8" t="n">
-        <v>136</v>
+        <v>604</v>
       </c>
       <c r="H8" t="n">
-        <v>38.02</v>
+        <v>23.59</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>415500</v>
+        <v>89900</v>
       </c>
       <c r="K8" t="n">
-        <v>407000</v>
+        <v>88700</v>
       </c>
       <c r="L8" t="n">
-        <v>413500</v>
+        <v>90400</v>
       </c>
       <c r="M8" t="n">
-        <v>404000</v>
+        <v>88000</v>
       </c>
       <c r="N8" t="n">
-        <v>37.82</v>
+        <v>23.65</v>
       </c>
       <c r="O8" t="n">
-        <v>17582214500</v>
+        <v>47878504200</v>
       </c>
       <c r="P8" t="n">
-        <v>822000</v>
+        <v>139200</v>
       </c>
       <c r="Q8" t="n">
-        <v>283000</v>
+        <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>-126000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>자동차 부품을 넘어 로봇 사업 확장 및 유럽 중국차 관세 이슈로 인한 호재. 글로벌 수주 기대.</t>
+          <t>에너지 대미 투자 협상 마무리 및 수주 잔고 규모 증가 관련 긍정적 전망. 월스트리트저널 보도 인용.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['로봇 사업', '유럽 관세', '글로벌 수주']</t>
+          <t>['수주잔고', '투자 협상', '에너지']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>89900</v>
+        <v>415500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.06</v>
+        <v>0.2</v>
       </c>
       <c r="E9" t="n">
-        <v>124</v>
+        <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>589</v>
+        <v>151</v>
       </c>
       <c r="H9" t="n">
-        <v>23.59</v>
+        <v>38.02</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>91700</v>
+        <v>417500</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1251,7 +1251,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>23.65</v>
+        <v>37.82</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1263,27 +1263,27 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>에너지 대미 투자 협상 마무리 및 수주 잔고 규모 증가 관련 긍정적 전망. 월스트리트저널 보도 인용.</t>
+          <t>차부품 넘어 로봇 사업 확장 및 유럽 중국차 관세 관련 호재. 아틀라스 관절부품 수주 및 글로벌 수주전 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['수주잔고', '투자 협상', '에너지']</t>
+          <t>['현대모비스', '로봇', '수주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>259000</v>
+        <v>14250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.72%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
-        <v>506</v>
+        <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>2709</v>
+        <v>284</v>
       </c>
       <c r="H10" t="n">
-        <v>46.71</v>
+        <v>5.98</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>269000</v>
+        <v>14320</v>
       </c>
       <c r="K10" t="n">
-        <v>258000</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>260000</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>257500</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>46.81</v>
+        <v>6.09</v>
       </c>
       <c r="O10" t="n">
-        <v>462813664500</v>
+        <v>45572000000</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>72100</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-174000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미증시 하락 및 매크로 변수 영향으로 인한 부정적 전망. 15만 전자 가능성 언급.</t>
+          <t>원전 관련 긍정적 재료 및 모건스탠리 매수세 언급. 상한가 및 급등 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['미증시 하락', '매크로 변수', '부정적 전망']</t>
+          <t>['우리기술', '원전', '모건스탠리']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1775000</v>
+        <v>19600</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.21%</t>
+          <t>-0.76%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.12</v>
+        <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>64</v>
       </c>
       <c r="F11" t="n">
-        <v>497</v>
+        <v>49</v>
       </c>
       <c r="G11" t="n">
-        <v>2000</v>
+        <v>224</v>
       </c>
       <c r="H11" t="n">
-        <v>50.55</v>
+        <v>10.65</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,28 +1423,28 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1853000</v>
+        <v>19750</v>
       </c>
       <c r="K11" t="n">
-        <v>1773000</v>
+        <v>19500</v>
       </c>
       <c r="L11" t="n">
-        <v>1785000</v>
+        <v>19840</v>
       </c>
       <c r="M11" t="n">
-        <v>1768000</v>
+        <v>19060</v>
       </c>
       <c r="N11" t="n">
-        <v>50.67</v>
+        <v>10.64</v>
       </c>
       <c r="O11" t="n">
-        <v>801119054000</v>
+        <v>38919720720</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>305500</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1454,20 +1454,20 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 증시 및 ADR 하락으로 인한 급락 우려. 오라클 실적 발표에 따른 변동성 예상.</t>
+          <t>NH투자증권의 목표가 상향 및 투자의견 '매수' 유지. 대차해지 독려 및 공매도 관련 긍정적 분위기.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['ADR 하락', '오라클 실적', '급락 우려']</t>
+          <t>['대우건설', 'NH투자증권', '목표주가']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7920</v>
+        <v>50400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.58%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="E12" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="G12" t="n">
-        <v>390</v>
+        <v>358</v>
       </c>
       <c r="H12" t="n">
-        <v>1.29</v>
+        <v>38.78</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>8300</v>
+        <v>50800</v>
       </c>
       <c r="K12" t="n">
-        <v>8400</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>7720</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.17</v>
+        <v>38.69</v>
       </c>
       <c r="O12" t="n">
-        <v>7916378225</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>21500</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-54000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>임상시험 디자인 및 기술 수출 기대감. 동시호가 3% 이상 시 상한가 확률 언급.</t>
+          <t>약 4.7조원 규모의 대규모 수주 공시가 확인되었으며, 이는 35억불 규모의 계약금액에 해당함. 사우디 및 베트남 관련 겹호재와 함께 외국인 매수세 유입이 관찰되어 상승 추세에 대한 기대감이 높음.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['임상시험', '기술 수출', '상한가 확률']</t>
+          <t>['수주', '공시', '외인 매수']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,97 +1568,373 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>233500</v>
+        <v>14310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-7.71%</t>
+          <t>-2.92%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.96</v>
+        <v>-0.39</v>
       </c>
       <c r="E13" t="n">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="F13" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>312</v>
+        <v>110</v>
       </c>
       <c r="H13" t="n">
-        <v>7.58</v>
+        <v>2.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>253000</v>
+        <v>14740</v>
       </c>
       <c r="K13" t="n">
-        <v>241000</v>
+        <v>14050</v>
       </c>
       <c r="L13" t="n">
-        <v>241000</v>
+        <v>14450</v>
       </c>
       <c r="M13" t="n">
-        <v>231000</v>
+        <v>14030</v>
       </c>
       <c r="N13" t="n">
-        <v>8.539999999999999</v>
+        <v>2.89</v>
       </c>
       <c r="O13" t="n">
-        <v>63859079250</v>
+        <v>17224430415</v>
       </c>
       <c r="P13" t="n">
-        <v>426000</v>
+        <v>31500</v>
       </c>
       <c r="Q13" t="n">
-        <v>86100</v>
+        <v>1272</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>163000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>CPI 예상치 하회에도 불구하고 주가 하락. 공매도 및 곽동신 오판에 대한 부정적 시각.</t>
+          <t>외국인 매수세 및 상승 기대감 존재. 단타 놀이터라는 부정적 의견 및 저점 분할 매수 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['대한광통신', '외국인', '단타']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>260500</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-3.16%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>800</v>
+      </c>
+      <c r="F14" t="n">
+        <v>506</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2607</v>
+      </c>
+      <c r="H14" t="n">
+        <v>46.71</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>269000</v>
+      </c>
+      <c r="K14" t="n">
+        <v>258000</v>
+      </c>
+      <c r="L14" t="n">
+        <v>261000</v>
+      </c>
+      <c r="M14" t="n">
+        <v>257500</v>
+      </c>
+      <c r="N14" t="n">
+        <v>46.81</v>
+      </c>
+      <c r="O14" t="n">
+        <v>563306002000</v>
+      </c>
+      <c r="P14" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>72100</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-396000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>미증시 하락 영향 및 레버리지 상품 관련 부정적 전망. AI 생태계 변화 관련 긍정 뉴스 언급.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
         <v>0.1</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>['CPI', '공매도', '주가 하락']</t>
-        </is>
-      </c>
-      <c r="X13" t="n">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['미증시', 'AI', '반도체']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>104</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1790000</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-3.56%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="E15" t="n">
+        <v>800</v>
+      </c>
+      <c r="F15" t="n">
+        <v>488</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1846</v>
+      </c>
+      <c r="H15" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>1856000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1013723000000</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>미국 증시 하락 및 SK하이닉스 ADR과의 괴리율에 대한 부정적 전망. 자사주 매수 언급.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['SK하이닉스', 'ADR', '미증시']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>69</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>한미반도체</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>234500</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-7.31%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="E16" t="n">
+        <v>101</v>
+      </c>
+      <c r="F16" t="n">
+        <v>61</v>
+      </c>
+      <c r="G16" t="n">
+        <v>344</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>253000</v>
+      </c>
+      <c r="K16" t="n">
+        <v>241000</v>
+      </c>
+      <c r="L16" t="n">
+        <v>241000</v>
+      </c>
+      <c r="M16" t="n">
+        <v>231000</v>
+      </c>
+      <c r="N16" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="O16" t="n">
+        <v>78384844750</v>
+      </c>
+      <c r="P16" t="n">
+        <v>426000</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>86100</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-152000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>주가 하락에 대한 개인 투자자들의 불만과 공매도 및 외국인 매도세에 대한 의심이 제기됨. 다만, 27만 안착 시 35만까지 상승 전망도 일부 존재.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['공매도', '주가 하락', '리벨런싱']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
         <v>1</v>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>042700</t>
         </is>

--- a/data/trending_integrated_20260911_09.xlsx
+++ b/data/trending_integrated_20260911_09.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>144300</v>
+        <v>141400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+24.08%</t>
+          <t>+22.21%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.26</v>
       </c>
       <c r="E2" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="H2" t="n">
         <v>4.32</v>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>116300</v>
+        <v>115700</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>112100</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>147500</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>112000</v>
       </c>
       <c r="N2" t="n">
         <v>4.58</v>
       </c>
       <c r="O2" t="n">
-        <v>229740000000</v>
+        <v>268941020000</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>196800</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>27750</v>
       </c>
       <c r="R2" t="n">
         <v>31000</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>MLCC 수요 폭발 및 무라타 관련 이슈로 인한 주가 상승 기대. 애플, 삼성전기 등 연관 언급.</t>
+          <t>MLCC 테마 및 일본 무라타 관련 소식으로 인한 급등세. 2차 상장 기대감 존재하나, 개미 꼬시기 및 차익실현 매물 경계 필요.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['MLCC', '삼화콘덴서', '무라타']</t>
+          <t>['MLCC', '무라타', '2차 상장']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,83 +655,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1967</v>
+        <v>29850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+11.76%</t>
+          <t>+14.37%</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E3" t="n">
+        <v>108</v>
+      </c>
+      <c r="F3" t="n">
+        <v>55</v>
+      </c>
+      <c r="G3" t="n">
+        <v>172</v>
+      </c>
+      <c r="H3" t="n">
         <v>0.32</v>
       </c>
-      <c r="E3" t="n">
-        <v>52</v>
-      </c>
-      <c r="F3" t="n">
-        <v>32</v>
-      </c>
-      <c r="G3" t="n">
-        <v>90</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.44</v>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1760</v>
+        <v>26100</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>26350</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>30300</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>25400</v>
       </c>
       <c r="N3" t="n">
-        <v>2.12</v>
+        <v>0.33</v>
       </c>
       <c r="O3" t="n">
-        <v>24556000000</v>
+        <v>160457664450</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>39350</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="R3" t="n">
-        <v>-846000</v>
+        <v>12000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>국제 유가 상승에 따른 전쟁 테마주 부각 및 2500원 목표 홀드 의견. 일부 부정적 의견 존재.</t>
+          <t>신규 상장주로서 조정 후 수급 개선 기대감. 2차 분할 매수 및 30분 내 추가 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['전쟁테마주', '국제유가', '흥아해운']</t>
+          <t>['신규 상장주', '수급 개선', '분할 매수']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28950</v>
+        <v>8300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+10.92%</t>
+          <t>+11.86%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.01</v>
+        <v>0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>109</v>
+        <v>442</v>
       </c>
       <c r="H4" t="n">
-        <v>0.32</v>
+        <v>1.29</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>26100</v>
+        <v>7420</v>
       </c>
       <c r="K4" t="n">
-        <v>26350</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>28950</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>25400</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.33</v>
+        <v>1.17</v>
       </c>
       <c r="O4" t="n">
-        <v>104372894700</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>39350</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>12000</v>
+        <v>16000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>신규 상장주로서 단기 조정 후 상승 기대감. 2차 번트 및 상한가 가능성 언급.</t>
+          <t>페니트리움바이오의 임상시험 디자인 및 9월 14일 WCLC에서의 데이터 발표 기대감. 기술 수출 가능성 및 제약 회사 급등 흐름 속에서 프로그램 매수 확인. 11.86%의 높은 상승률 기록.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['스카이랩스', '신규주', '수급']</t>
+          <t>['임상시험', '기술수출', '데이터발표']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10170</v>
+        <v>16050</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+9.59%</t>
+          <t>+10.61%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.07000000000000001</v>
+        <v>3.11</v>
       </c>
       <c r="E5" t="n">
-        <v>43</v>
+        <v>215</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>136</v>
       </c>
       <c r="G5" t="n">
-        <v>150</v>
+        <v>567</v>
       </c>
       <c r="H5" t="n">
-        <v>4.49</v>
+        <v>3.14</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9280</v>
+        <v>14510</v>
       </c>
       <c r="K5" t="n">
-        <v>10030</v>
+        <v>17010</v>
       </c>
       <c r="L5" t="n">
-        <v>10880</v>
+        <v>17310</v>
       </c>
       <c r="M5" t="n">
-        <v>10010</v>
+        <v>15600</v>
       </c>
       <c r="N5" t="n">
-        <v>4.42</v>
+        <v>0.03</v>
       </c>
       <c r="O5" t="n">
-        <v>15077490565</v>
+        <v>117214206775</v>
       </c>
       <c r="P5" t="n">
-        <v>15640</v>
+        <v>36200</v>
       </c>
       <c r="Q5" t="n">
-        <v>5470</v>
+        <v>8920</v>
       </c>
       <c r="R5" t="n">
-        <v>-6000</v>
+        <v>-268000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>프리갈리앙 베스트 의료기술상 수상 및 탈모약 관련 이슈. 호재 뉴스에도 주가 하락 가능성 언급.</t>
+          <t>중동 전쟁 및 유가 폭등으로 인한 급등 기대감. WTI 100달러 돌파 및 3연상 목표.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['바이오니아', '프리갈리앙', '탈모약']</t>
+          <t>['유가 폭등', '중동 전쟁', '3연상']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15890</v>
+        <v>10120</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+9.51%</t>
+          <t>+9.05%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>200</v>
+        <v>45</v>
       </c>
       <c r="F6" t="n">
-        <v>127</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>572</v>
+        <v>168</v>
       </c>
       <c r="H6" t="n">
-        <v>3.14</v>
+        <v>4.49</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14510</v>
+        <v>9280</v>
       </c>
       <c r="K6" t="n">
-        <v>17010</v>
+        <v>10030</v>
       </c>
       <c r="L6" t="n">
-        <v>17310</v>
+        <v>10880</v>
       </c>
       <c r="M6" t="n">
-        <v>15690</v>
+        <v>10010</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03</v>
+        <v>4.42</v>
       </c>
       <c r="O6" t="n">
-        <v>106942896195</v>
+        <v>15861326715</v>
       </c>
       <c r="P6" t="n">
-        <v>36200</v>
+        <v>15640</v>
       </c>
       <c r="Q6" t="n">
-        <v>8920</v>
+        <v>5470</v>
       </c>
       <c r="R6" t="n">
-        <v>-268000</v>
+        <v>-6000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>중동 전쟁 및 유가 폭등으로 인한 급등 기대감. WTI 100달러 돌파 및 3연상 목표.</t>
+          <t>프리갈리앙 코리아 수상 및 베스트 의료기술상 수상. 공매도 세력과의 경쟁 및 역대급 거래량 기대감, 그러나 호재 뉴스 대비 주가 움직임 지연 우려.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['유가 폭등', '중동 전쟁', '3연상']</t>
+          <t>['프리갈리앙', '의료기술상', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,77 +1016,77 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7890</v>
+        <v>1979</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+6.33%</t>
+          <t>+4.10%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="E7" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="F7" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>407</v>
+        <v>94</v>
       </c>
       <c r="H7" t="n">
-        <v>1.29</v>
+        <v>2.44</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7420</v>
+        <v>1901</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2050</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2080</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1950</v>
       </c>
       <c r="N7" t="n">
-        <v>1.17</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>8749000000</v>
+        <v>26499197970</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4795</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1524</v>
       </c>
       <c r="R7" t="n">
-        <v>16000</v>
+        <v>-846000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>임상시험 디자인 및 기술 수출 기대감. 동시호가 3% 이상 시 상한가 확률 언급.</t>
+          <t>국제 유가 상승 및 전쟁 테마주로 부각되며 2500원까지 홀드 전망. 그러나 외국인 매도세 및 차익실현 매물 출회 가능성 상존.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['임상시험', '기술 수출', '상한가 확률']</t>
+          <t>['전쟁 테마주', '국제 유가', '외국인 매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>89700</v>
+        <v>253000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.06</v>
+        <v>-0.96</v>
       </c>
       <c r="E8" t="n">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="F8" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="G8" t="n">
-        <v>604</v>
+        <v>397</v>
       </c>
       <c r="H8" t="n">
-        <v>23.59</v>
+        <v>7.58</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>89900</v>
+        <v>250500</v>
       </c>
       <c r="K8" t="n">
-        <v>88700</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>90400</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>23.65</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>47878504200</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>139200</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-126000</v>
+        <v>-152000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>에너지 대미 투자 협상 마무리 및 수주 잔고 규모 증가 관련 긍정적 전망. 월스트리트저널 보도 인용.</t>
+          <t>기관 매도세 및 공매도 압박으로 인한 급락세. CPI 발표 및 유가 변동성으로 인한 조정 국면, 개미 털기 및 패턴 반복 경계.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['수주잔고', '투자 협상', '에너지']</t>
+          <t>['기관 매도', '공매도', 'CPI']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>415500</v>
+        <v>89600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.2</v>
+        <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>59</v>
+        <v>141</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="G9" t="n">
-        <v>151</v>
+        <v>633</v>
       </c>
       <c r="H9" t="n">
-        <v>38.02</v>
+        <v>23.59</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>417500</v>
+        <v>89900</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>88700</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>90400</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="N9" t="n">
-        <v>37.82</v>
+        <v>23.65</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>52858871050</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>139200</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="R9" t="n">
-        <v>4000</v>
+        <v>-126000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>차부품 넘어 로봇 사업 확장 및 유럽 중국차 관세 관련 호재. 아틀라스 관절부품 수주 및 글로벌 수주전 기대.</t>
+          <t>미국 투자 협상 마무리 및 중동 에너지 공급망 이슈로 인한 원전주 수급 쏠림 기대. 반기보고서 기준 수주잔고 29.7조원. 다만, 야간 선물 폭락 및 일부 하락 예측도 존재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['현대모비스', '로봇', '수주']</t>
+          <t>['수주잔고', '투자협상', '원전주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14250</v>
+        <v>50000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.11</v>
+        <v>0.09</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="G10" t="n">
-        <v>284</v>
+        <v>368</v>
       </c>
       <c r="H10" t="n">
-        <v>5.98</v>
+        <v>38.78</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14320</v>
+        <v>50400</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>50500</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>50600</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>49650</v>
       </c>
       <c r="N10" t="n">
-        <v>6.09</v>
+        <v>38.69</v>
       </c>
       <c r="O10" t="n">
-        <v>45572000000</v>
+        <v>26136184925</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>67300</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>23150</v>
       </c>
       <c r="R10" t="n">
-        <v>-174000</v>
+        <v>-54000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>원전 관련 긍정적 재료 및 모건스탠리 매수세 언급. 상한가 및 급등 기대감.</t>
+          <t>사우디 및 베트남 관련 35억불 규모 대형 수주 공시. 상승 추세 진입 및 외인 매수세 유입으로 인한 추가 상승 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['우리기술', '원전', '모건스탠리']</t>
+          <t>['대형 수주', '사우디', '베트남']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19600</v>
+        <v>19580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.76%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F11" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="H11" t="n">
         <v>10.65</v>
@@ -1438,7 +1438,7 @@
         <v>10.64</v>
       </c>
       <c r="O11" t="n">
-        <v>38919720720</v>
+        <v>43638596050</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>NH투자증권의 목표가 상향 및 투자의견 '매수' 유지. 대차해지 독려 및 공매도 관련 긍정적 분위기.</t>
+          <t>NH투자증권 목표주가 상향 (3만원) 및 신규 투자 협상 마무리 기대감. 대차해지 독려 및 공매도 세력과의 경쟁 구도 형성.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['대우건설', 'NH투자증권', '목표주가']</t>
+          <t>['NH투자증권', '목표주가 상향', '대차해지']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50400</v>
+        <v>411500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="E12" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="F12" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>358</v>
+        <v>157</v>
       </c>
       <c r="H12" t="n">
-        <v>38.78</v>
+        <v>38.02</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>50800</v>
+        <v>415500</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>407000</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>415000</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>404000</v>
       </c>
       <c r="N12" t="n">
-        <v>38.69</v>
+        <v>37.82</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>20550879750</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>822000</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>283000</v>
       </c>
       <c r="R12" t="n">
-        <v>-54000</v>
+        <v>4000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모의 대규모 수주 공시가 확인되었으며, 이는 35억불 규모의 계약금액에 해당함. 사우디 및 베트남 관련 겹호재와 함께 외국인 매수세 유입이 관찰되어 상승 추세에 대한 기대감이 높음.</t>
+          <t>차부품 넘어 로봇 사업 확장 및 유럽 중국차 관세 관련 호재. 아틀라스 관절부품 수주 및 글로벌 수주전 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['수주', '공시', '외인 매수']</t>
+          <t>['현대모비스', '로봇', '수주']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14310</v>
+        <v>14220</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.92%</t>
+          <t>-2.60%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.39</v>
+        <v>-0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="G13" t="n">
-        <v>110</v>
+        <v>319</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5</v>
+        <v>5.98</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14740</v>
+        <v>14600</v>
       </c>
       <c r="K13" t="n">
-        <v>14050</v>
+        <v>14800</v>
       </c>
       <c r="L13" t="n">
-        <v>14450</v>
+        <v>14950</v>
       </c>
       <c r="M13" t="n">
-        <v>14030</v>
+        <v>14020</v>
       </c>
       <c r="N13" t="n">
-        <v>2.89</v>
+        <v>6.09</v>
       </c>
       <c r="O13" t="n">
-        <v>17224430415</v>
+        <v>49700728020</v>
       </c>
       <c r="P13" t="n">
-        <v>31500</v>
+        <v>30200</v>
       </c>
       <c r="Q13" t="n">
-        <v>1272</v>
+        <v>3540</v>
       </c>
       <c r="R13" t="n">
-        <v>163000</v>
+        <v>-174000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>외국인 매수세 및 상승 기대감 존재. 단타 놀이터라는 부정적 의견 및 저점 분할 매수 언급.</t>
+          <t>원전 관련 긍정적 재료 및 모건스탠리 매수세 언급. 상한가 및 급등 기대감.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['대한광통신', '외국인', '단타']</t>
+          <t>['우리기술', '원전', '모건스탠리']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>260500</v>
+        <v>14270</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.16%</t>
+          <t>-3.19%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.1</v>
+        <v>-0.39</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>41</v>
       </c>
       <c r="F14" t="n">
-        <v>506</v>
+        <v>25</v>
       </c>
       <c r="G14" t="n">
-        <v>2607</v>
+        <v>120</v>
       </c>
       <c r="H14" t="n">
-        <v>46.71</v>
+        <v>2.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>269000</v>
+        <v>14740</v>
       </c>
       <c r="K14" t="n">
-        <v>258000</v>
+        <v>14050</v>
       </c>
       <c r="L14" t="n">
-        <v>261000</v>
+        <v>14450</v>
       </c>
       <c r="M14" t="n">
-        <v>257500</v>
+        <v>14030</v>
       </c>
       <c r="N14" t="n">
-        <v>46.81</v>
+        <v>2.89</v>
       </c>
       <c r="O14" t="n">
-        <v>563306002000</v>
+        <v>19443079820</v>
       </c>
       <c r="P14" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q14" t="n">
-        <v>72100</v>
+        <v>1272</v>
       </c>
       <c r="R14" t="n">
-        <v>-396000</v>
+        <v>163000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미증시 하락 영향 및 레버리지 상품 관련 부정적 전망. AI 생태계 변화 관련 긍정 뉴스 언급.</t>
+          <t>외국인 순매수 유입 및 20% 상승 가능성 언급. 금리 인상 및 국장 전반 하락세 속에서 저점 매수 기회 포착.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['미증시', 'AI', '반도체']</t>
+          <t>['외국인 순매수', '금리 인상', '저점 매수']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1790000</v>
+        <v>259500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.56%</t>
+          <t>-3.53%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="E15" t="n">
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="G15" t="n">
-        <v>1846</v>
+        <v>2526</v>
       </c>
       <c r="H15" t="n">
-        <v>50.55</v>
+        <v>46.71</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1856000</v>
+        <v>269000</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>258000</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>261000</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>257500</v>
       </c>
       <c r="N15" t="n">
-        <v>50.67</v>
+        <v>46.81</v>
       </c>
       <c r="O15" t="n">
-        <v>1013723000000</v>
+        <v>666404904250</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>72100</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>-396000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 증시 하락 및 SK하이닉스 ADR과의 괴리율에 대한 부정적 전망. 자사주 매수 언급.</t>
+          <t>미 증시 하락 영향으로 급락세. AI 생태계 변화 및 반도체 수급 폭발 가능성 뉴스 언급되나, 단기적 하락 전망 우세.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['SK하이닉스', 'ADR', '미증시']</t>
+          <t>['AI 생태계', '반도체 수급', '미 증시']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>234500</v>
+        <v>1780000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-7.31%</t>
+          <t>-3.94%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.96</v>
+        <v>-0.12</v>
       </c>
       <c r="E16" t="n">
-        <v>101</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>61</v>
+        <v>475</v>
       </c>
       <c r="G16" t="n">
-        <v>344</v>
+        <v>1721</v>
       </c>
       <c r="H16" t="n">
-        <v>7.58</v>
+        <v>50.55</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>253000</v>
+        <v>1853000</v>
       </c>
       <c r="K16" t="n">
-        <v>241000</v>
+        <v>1773000</v>
       </c>
       <c r="L16" t="n">
-        <v>241000</v>
+        <v>1795000</v>
       </c>
       <c r="M16" t="n">
-        <v>231000</v>
+        <v>1768000</v>
       </c>
       <c r="N16" t="n">
-        <v>8.539999999999999</v>
+        <v>50.67</v>
       </c>
       <c r="O16" t="n">
-        <v>78384844750</v>
+        <v>1161339962500</v>
       </c>
       <c r="P16" t="n">
-        <v>426000</v>
+        <v>2987000</v>
       </c>
       <c r="Q16" t="n">
-        <v>86100</v>
+        <v>305500</v>
       </c>
       <c r="R16" t="n">
-        <v>-152000</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 개인 투자자들의 불만과 공매도 및 외국인 매도세에 대한 의심이 제기됨. 다만, 27만 안착 시 35만까지 상승 전망도 일부 존재.</t>
+          <t>미국 증시 급락 및 오라클 실적 발표 혼조세. AI 클라우드 수요 증가 뉴스에도 불구하고 단기적 하락세 지속 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['공매도', '주가 하락', '리벨런싱']</t>
+          <t>['오라클 실적', 'AI 클라우드', '미 증시']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>000660</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260911_09.xlsx
+++ b/data/trending_integrated_20260911_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:Z17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,70 +563,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>141400</v>
+        <v>16130</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+22.21%</t>
+          <t>+33.42%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.26</v>
+        <v>3.11</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>219</v>
       </c>
       <c r="F2" t="n">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="G2" t="n">
-        <v>81</v>
+        <v>577</v>
       </c>
       <c r="H2" t="n">
-        <v>4.32</v>
+        <v>3.14</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>115700</v>
+        <v>12090</v>
       </c>
       <c r="K2" t="n">
-        <v>112100</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>147500</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>112000</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>4.58</v>
+        <v>0.03</v>
       </c>
       <c r="O2" t="n">
-        <v>268941020000</v>
+        <v>132911000000</v>
       </c>
       <c r="P2" t="n">
-        <v>196800</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>27750</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>31000</v>
+        <v>-268000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>MLCC 테마 및 일본 무라타 관련 소식으로 인한 급등세. 2차 상장 기대감 존재하나, 개미 꼬시기 및 차익실현 매물 경계 필요.</t>
+          <t>중동 전쟁 및 유가 폭등으로 인한 급등 기대감. WTI 100달러 돌파 및 3연상 목표.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,11 +635,11 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['MLCC', '무라타', '2차 상장']</t>
+          <t>['유가 폭등', '중동 전쟁', '3연상']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29850</v>
+        <v>139200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+14.37%</t>
+          <t>+19.69%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.01</v>
+        <v>-0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>172</v>
+        <v>91</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32</v>
+        <v>4.32</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>26100</v>
+        <v>116300</v>
       </c>
       <c r="K3" t="n">
-        <v>26350</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>30300</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>25400</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.33</v>
+        <v>4.58</v>
       </c>
       <c r="O3" t="n">
-        <v>160457664450</v>
+        <v>297888000000</v>
       </c>
       <c r="P3" t="n">
-        <v>39350</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>12000</v>
+        <v>31000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>신규 상장주로서 조정 후 수급 개선 기대감. 2차 분할 매수 및 30분 내 추가 상승 가능성 언급.</t>
+          <t>MLCC 관련 무라타 생산 이슈 및 애플 관련주로 부각되며 급등 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['신규 상장주', '수급 개선', '분할 매수']</t>
+          <t>['MLCC', '무라타', '애플']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,46 +740,46 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>001820</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8300</v>
+        <v>1968</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+11.86%</t>
+          <t>+11.82%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="E4" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>442</v>
+        <v>88</v>
       </c>
       <c r="H4" t="n">
-        <v>1.29</v>
+        <v>2.44</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7420</v>
+        <v>1760</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.17</v>
+        <v>2.12</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>28644000000</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -803,27 +803,27 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>16000</v>
+        <v>-846000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>페니트리움바이오의 임상시험 디자인 및 9월 14일 WCLC에서의 데이터 발표 기대감. 기술 수출 가능성 및 제약 회사 급등 흐름 속에서 프로그램 매수 확인. 11.86%의 높은 상승률 기록.</t>
+          <t>국제 유가 상승 및 전쟁 테마 관련주로 부각되며 매수세 유입 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['임상시험', '기술수출', '데이터발표']</t>
+          <t>['전쟁 테마주', '국제 유가', '홍해']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16050</v>
+        <v>9930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+10.61%</t>
+          <t>+7.00%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>215</v>
+        <v>46</v>
       </c>
       <c r="F5" t="n">
-        <v>136</v>
+        <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>567</v>
+        <v>177</v>
       </c>
       <c r="H5" t="n">
-        <v>3.14</v>
+        <v>4.49</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14510</v>
+        <v>9280</v>
       </c>
       <c r="K5" t="n">
-        <v>17010</v>
+        <v>10030</v>
       </c>
       <c r="L5" t="n">
-        <v>17310</v>
+        <v>10880</v>
       </c>
       <c r="M5" t="n">
-        <v>15600</v>
+        <v>9880</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03</v>
+        <v>4.42</v>
       </c>
       <c r="O5" t="n">
-        <v>117214206775</v>
+        <v>17009444345</v>
       </c>
       <c r="P5" t="n">
-        <v>36200</v>
+        <v>15640</v>
       </c>
       <c r="Q5" t="n">
-        <v>8920</v>
+        <v>5470</v>
       </c>
       <c r="R5" t="n">
-        <v>-268000</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>중동 전쟁 및 유가 폭등으로 인한 급등 기대감. WTI 100달러 돌파 및 3연상 목표.</t>
+          <t>프리갈리앙 베스트 의료기술상 수상 소식 기반, 거래량 증가하며 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유가 폭등', '중동 전쟁', '3연상']</t>
+          <t>['프리갈리앙', '의료 기술상', '거래량']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10120</v>
+        <v>14230</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+9.05%</t>
+          <t>-0.63%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="E6" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>168</v>
+        <v>331</v>
       </c>
       <c r="H6" t="n">
-        <v>4.49</v>
+        <v>5.98</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>9280</v>
+        <v>14320</v>
       </c>
       <c r="K6" t="n">
-        <v>10030</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>10880</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>10010</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.42</v>
+        <v>6.09</v>
       </c>
       <c r="O6" t="n">
-        <v>15861326715</v>
+        <v>53960000000</v>
       </c>
       <c r="P6" t="n">
-        <v>15640</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>5470</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-6000</v>
+        <v>-174000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>프리갈리앙 코리아 수상 및 베스트 의료기술상 수상. 공매도 세력과의 경쟁 및 역대급 거래량 기대감, 그러나 호재 뉴스 대비 주가 움직임 지연 우려.</t>
+          <t>원전 관련 긍정적 재료 및 모건스탠리 매수세 언급. 상한가 및 급등 기대감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['프리갈리앙', '의료기술상', '공매도']</t>
+          <t>['우리기술', '원전', '모건스탠리']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1979</v>
+        <v>50000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+4.10%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.32</v>
+        <v>0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="G7" t="n">
-        <v>94</v>
+        <v>377</v>
       </c>
       <c r="H7" t="n">
-        <v>2.44</v>
+        <v>38.78</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1901</v>
+        <v>50400</v>
       </c>
       <c r="K7" t="n">
-        <v>2050</v>
+        <v>50500</v>
       </c>
       <c r="L7" t="n">
-        <v>2080</v>
+        <v>50600</v>
       </c>
       <c r="M7" t="n">
-        <v>1950</v>
+        <v>49650</v>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>38.69</v>
       </c>
       <c r="O7" t="n">
-        <v>26499197970</v>
+        <v>28589018250</v>
       </c>
       <c r="P7" t="n">
-        <v>4795</v>
+        <v>67300</v>
       </c>
       <c r="Q7" t="n">
-        <v>1524</v>
+        <v>23150</v>
       </c>
       <c r="R7" t="n">
-        <v>-846000</v>
+        <v>-54000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>국제 유가 상승 및 전쟁 테마주로 부각되며 2500원까지 홀드 전망. 그러나 외국인 매도세 및 차익실현 매물 출회 가능성 상존.</t>
+          <t>사우디 및 베트남 관련 35억불 규모 대형 수주 공시. 상승 추세 진입 및 외인 매수세 유입으로 인한 추가 상승 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['전쟁 테마주', '국제 유가', '외국인 매도']</t>
+          <t>['대형 수주', '사우디', '베트남']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>253000</v>
+        <v>412000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.96</v>
+        <v>0.2</v>
       </c>
       <c r="E8" t="n">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="F8" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="G8" t="n">
-        <v>397</v>
+        <v>159</v>
       </c>
       <c r="H8" t="n">
-        <v>7.58</v>
+        <v>38.02</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>250500</v>
+        <v>415500</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>407000</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>415000</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>404000</v>
       </c>
       <c r="N8" t="n">
-        <v>8.539999999999999</v>
+        <v>37.82</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>21999657750</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>822000</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>283000</v>
       </c>
       <c r="R8" t="n">
-        <v>-152000</v>
+        <v>4000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>기관 매도세 및 공매도 압박으로 인한 급락세. CPI 발표 및 유가 변동성으로 인한 조정 국면, 개미 털기 및 패턴 반복 경계.</t>
+          <t>차부품 넘어 로봇 사업 확장 및 유럽 중국차 관세 관련 호재. 아틀라스 관절부품 수주 및 글로벌 수주전 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['기관 매도', '공매도', 'CPI']</t>
+          <t>['현대모비스', '로봇', '수주']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>89600</v>
+        <v>19490</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>-1.32%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.06</v>
+        <v>0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="F9" t="n">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="G9" t="n">
-        <v>633</v>
+        <v>244</v>
       </c>
       <c r="H9" t="n">
-        <v>23.59</v>
+        <v>10.65</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>89900</v>
+        <v>19750</v>
       </c>
       <c r="K9" t="n">
-        <v>88700</v>
+        <v>19500</v>
       </c>
       <c r="L9" t="n">
-        <v>90400</v>
+        <v>19840</v>
       </c>
       <c r="M9" t="n">
-        <v>88000</v>
+        <v>19060</v>
       </c>
       <c r="N9" t="n">
-        <v>23.65</v>
+        <v>10.64</v>
       </c>
       <c r="O9" t="n">
-        <v>52858871050</v>
+        <v>48316030380</v>
       </c>
       <c r="P9" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>-126000</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 투자 협상 마무리 및 중동 에너지 공급망 이슈로 인한 원전주 수급 쏠림 기대. 반기보고서 기준 수주잔고 29.7조원. 다만, 야간 선물 폭락 및 일부 하락 예측도 존재.</t>
+          <t>NH투자증권 목표가 상향 조정 및 자사주 소각 이벤트 기반 상승 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['수주잔고', '투자협상', '원전주']</t>
+          <t>['NH투자증권', '목표주가', '자사주 소각']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50000</v>
+        <v>14740</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.09</v>
+        <v>-0.39</v>
       </c>
       <c r="E10" t="n">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="F10" t="n">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="G10" t="n">
-        <v>368</v>
+        <v>128</v>
       </c>
       <c r="H10" t="n">
-        <v>38.78</v>
+        <v>2.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>50400</v>
+        <v>14960</v>
       </c>
       <c r="K10" t="n">
-        <v>50500</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>50600</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>49650</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>38.69</v>
+        <v>2.89</v>
       </c>
       <c r="O10" t="n">
-        <v>26136184925</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>67300</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>23150</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-54000</v>
+        <v>163000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>사우디 및 베트남 관련 35억불 규모 대형 수주 공시. 상승 추세 진입 및 외인 매수세 유입으로 인한 추가 상승 기대감.</t>
+          <t>외국인 순매수 유입 및 20% 상승 가능성 언급. 금리 인상 및 국장 전반 하락세 속에서 저점 매수 기회 포착.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['대형 수주', '사우디', '베트남']</t>
+          <t>['외국인 순매수', '금리 인상', '저점 매수']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19580</v>
+        <v>89900</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>145</v>
       </c>
       <c r="F11" t="n">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="G11" t="n">
-        <v>240</v>
+        <v>654</v>
       </c>
       <c r="H11" t="n">
-        <v>10.65</v>
+        <v>23.59</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>19750</v>
+        <v>91700</v>
       </c>
       <c r="K11" t="n">
-        <v>19500</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>19840</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>19060</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>10.64</v>
+        <v>23.65</v>
       </c>
       <c r="O11" t="n">
-        <v>43638596050</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>-126000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>NH투자증권 목표주가 상향 (3만원) 및 신규 투자 협상 마무리 기대감. 대차해지 독려 및 공매도 세력과의 경쟁 구도 형성.</t>
+          <t>미국 투자 협상 마무리 및 중동 에너지 공급망 이슈로 원전주 부각, 수주 잔고 기반 급등 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['NH투자증권', '목표주가 상향', '대차해지']</t>
+          <t>['원전주', '에너지 공급망', '수주 잔고']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>411500</v>
+        <v>29650</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>-2.15%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.2</v>
+        <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>62</v>
+        <v>126</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="G12" t="n">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="H12" t="n">
-        <v>38.02</v>
+        <v>0.32</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>415500</v>
+        <v>30300</v>
       </c>
       <c r="K12" t="n">
-        <v>407000</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>415000</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>404000</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>37.82</v>
+        <v>0.33</v>
       </c>
       <c r="O12" t="n">
-        <v>20550879750</v>
+        <v>190583000000</v>
       </c>
       <c r="P12" t="n">
-        <v>822000</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>283000</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>차부품 넘어 로봇 사업 확장 및 유럽 중국차 관세 관련 호재. 아틀라스 관절부품 수주 및 글로벌 수주전 기대.</t>
+          <t>신규 상장주로서 단기 조정 후 수급 개선 및 상승 기대감 형성.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['현대모비스', '로봇', '수주']</t>
+          <t>['신규주', '수급', '조정']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14220</v>
+        <v>8050</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.60%</t>
+          <t>-3.01%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.11</v>
+        <v>0.12</v>
       </c>
       <c r="E13" t="n">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="F13" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G13" t="n">
-        <v>319</v>
+        <v>490</v>
       </c>
       <c r="H13" t="n">
-        <v>5.98</v>
+        <v>1.29</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14600</v>
+        <v>8300</v>
       </c>
       <c r="K13" t="n">
-        <v>14800</v>
+        <v>8400</v>
       </c>
       <c r="L13" t="n">
-        <v>14950</v>
+        <v>8700</v>
       </c>
       <c r="M13" t="n">
-        <v>14020</v>
+        <v>7720</v>
       </c>
       <c r="N13" t="n">
-        <v>6.09</v>
+        <v>1.17</v>
       </c>
       <c r="O13" t="n">
-        <v>49700728020</v>
+        <v>10536617170</v>
       </c>
       <c r="P13" t="n">
-        <v>30200</v>
+        <v>21500</v>
       </c>
       <c r="Q13" t="n">
-        <v>3540</v>
+        <v>2300</v>
       </c>
       <c r="R13" t="n">
-        <v>-174000</v>
+        <v>16000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>원전 관련 긍정적 재료 및 모건스탠리 매수세 언급. 상한가 및 급등 기대감.</t>
+          <t>14일 WCLC 센딥파텔 교수의 미친 데이터 발표 기대감. 기술 수출 몇조 가능성 및 종가 보합 예상.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['우리기술', '원전', '모건스탠리']</t>
+          <t>['임상시험', '데이터 발표', '기술 수출']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14270</v>
+        <v>7440</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.19%</t>
+          <t>-3.12%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.39</v>
+        <v>0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G14" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5</v>
+        <v>11.72</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14740</v>
+        <v>7680</v>
       </c>
       <c r="K14" t="n">
-        <v>14050</v>
+        <v>7540</v>
       </c>
       <c r="L14" t="n">
-        <v>14450</v>
+        <v>7660</v>
       </c>
       <c r="M14" t="n">
-        <v>14030</v>
+        <v>7400</v>
       </c>
       <c r="N14" t="n">
-        <v>2.89</v>
+        <v>11.62</v>
       </c>
       <c r="O14" t="n">
-        <v>19443079820</v>
+        <v>5234466110</v>
       </c>
       <c r="P14" t="n">
-        <v>31500</v>
+        <v>8850</v>
       </c>
       <c r="Q14" t="n">
-        <v>1272</v>
+        <v>4220</v>
       </c>
       <c r="R14" t="n">
-        <v>163000</v>
+        <v>150000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>외국인 순매수 유입 및 20% 상승 가능성 언급. 금리 인상 및 국장 전반 하락세 속에서 저점 매수 기회 포착.</t>
+          <t>기관 및 외국인 순매수 전환 신호 포착, 단기 등락 변동성 확대 예상.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['외국인 순매수', '금리 인상', '저점 매수']</t>
+          <t>['기관', '외국인', '수급']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>259500</v>
+        <v>259000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.53%</t>
+          <t>-3.72%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="G15" t="n">
-        <v>2526</v>
+        <v>2396</v>
       </c>
       <c r="H15" t="n">
         <v>46.71</v>
@@ -1806,7 +1806,7 @@
         <v>46.81</v>
       </c>
       <c r="O15" t="n">
-        <v>666404904250</v>
+        <v>786011780750</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미 증시 하락 영향으로 급락세. AI 생태계 변화 및 반도체 수급 폭발 가능성 뉴스 언급되나, 단기적 하락 전망 우세.</t>
+          <t>거시 경제 요인 및 FOMC 경계감 속 단기 하락 전망, 일부 긍정적 전망 혼재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI 생태계', '반도체 수급', '미 증시']</t>
+          <t>['거시 경제', 'FOMC', '국내 증시']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1780000</v>
+        <v>1781000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.94%</t>
+          <t>-3.89%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="G16" t="n">
-        <v>1721</v>
+        <v>1522</v>
       </c>
       <c r="H16" t="n">
         <v>50.55</v>
@@ -1898,7 +1898,7 @@
         <v>50.67</v>
       </c>
       <c r="O16" t="n">
-        <v>1161339962500</v>
+        <v>1322587596500</v>
       </c>
       <c r="P16" t="n">
         <v>2987000</v>
@@ -1907,23 +1907,23 @@
         <v>305500</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>-115000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 증시 급락 및 오라클 실적 발표 혼조세. AI 클라우드 수요 증가 뉴스에도 불구하고 단기적 하락세 지속 전망.</t>
+          <t>오라클 실적 발표 기반 단기 반등 기대 있으나, 거시 경제 악재 및 하락 압력 지속.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['오라클 실적', 'AI 클라우드', '미 증시']</t>
+          <t>['오라클', 'AI 클라우드', '거시 경제']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1937,6 +1937,98 @@
       <c r="Z16" t="inlineStr">
         <is>
           <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>한미반도체</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>232500</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-8.10%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="E17" t="n">
+        <v>122</v>
+      </c>
+      <c r="F17" t="n">
+        <v>69</v>
+      </c>
+      <c r="G17" t="n">
+        <v>428</v>
+      </c>
+      <c r="H17" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>253000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>241000</v>
+      </c>
+      <c r="L17" t="n">
+        <v>241000</v>
+      </c>
+      <c r="M17" t="n">
+        <v>231000</v>
+      </c>
+      <c r="N17" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="O17" t="n">
+        <v>99828706250</v>
+      </c>
+      <c r="P17" t="n">
+        <v>426000</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>86100</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-152000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>CPI 발표 및 거시 경제 악재로 인한 단기 급락, 공매도 세력 영향 및 투자 심리 위축.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>['CPI', '공매도', 'HBM']</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>042700</t>
         </is>
       </c>
     </row>
